--- a/data/trending_integrated_20260909_09.xlsx
+++ b/data/trending_integrated_20260909_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15250</v>
+        <v>13300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+11.31%</t>
+          <t>+12.62%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.39</v>
+        <v>0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>287</v>
+        <v>382</v>
       </c>
       <c r="H2" t="n">
-        <v>1.55</v>
+        <v>5.64</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>13700</v>
+        <v>11810</v>
       </c>
       <c r="K2" t="n">
-        <v>14260</v>
+        <v>12050</v>
       </c>
       <c r="L2" t="n">
-        <v>15300</v>
+        <v>13990</v>
       </c>
       <c r="M2" t="n">
-        <v>14210</v>
+        <v>11950</v>
       </c>
       <c r="N2" t="n">
-        <v>1.94</v>
+        <v>5.42</v>
       </c>
       <c r="O2" t="n">
-        <v>109644678625</v>
+        <v>119536095005</v>
       </c>
       <c r="P2" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q2" t="n">
-        <v>1252</v>
+        <v>3540</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>731000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등 영향. 투명거래 규제 해제 후 기대감.</t>
+          <t>원전 및 로봇 섹터 주도주 전망. 미국 원전 관련 뉴스 및 소형원자로 배치 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '차트']</t>
+          <t>['원전', '로봇', '소형원자로']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32800</v>
+        <v>55200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+10.25%</t>
+          <t>+12.08%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31</v>
+        <v>14.96</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>29750</v>
+        <v>49250</v>
       </c>
       <c r="K3" t="n">
-        <v>31600</v>
+        <v>53500</v>
       </c>
       <c r="L3" t="n">
-        <v>34200</v>
+        <v>55900</v>
       </c>
       <c r="M3" t="n">
-        <v>31300</v>
+        <v>51600</v>
       </c>
       <c r="N3" t="n">
-        <v>0.23</v>
+        <v>14.93</v>
       </c>
       <c r="O3" t="n">
-        <v>103622203825</v>
+        <v>47421466300</v>
       </c>
       <c r="P3" t="n">
-        <v>39350</v>
+        <v>108900</v>
       </c>
       <c r="Q3" t="n">
-        <v>8200</v>
+        <v>18230</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-198000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>상장폐지 우려 및 주가 급락 전망. 개인 투자자 탈출 권유.</t>
+          <t>외인 매도세 속 목표가 상향 및 성장성 기대. 수소 에너지 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['상장폐지', '주가', '탈출']</t>
+          <t>['수소에너지', '목표가', '성장성']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53300</v>
+        <v>4025</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+8.22%</t>
+          <t>+10.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03</v>
+        <v>2.74</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>228</v>
       </c>
       <c r="H4" t="n">
-        <v>14.96</v>
+        <v>3.19</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>49250</v>
+        <v>3640</v>
       </c>
       <c r="K4" t="n">
-        <v>53500</v>
+        <v>3750</v>
       </c>
       <c r="L4" t="n">
-        <v>55500</v>
+        <v>4460</v>
       </c>
       <c r="M4" t="n">
-        <v>51600</v>
+        <v>3680</v>
       </c>
       <c r="N4" t="n">
-        <v>14.93</v>
+        <v>0.45</v>
       </c>
       <c r="O4" t="n">
-        <v>28186189200</v>
+        <v>181903605956</v>
       </c>
       <c r="P4" t="n">
-        <v>108900</v>
+        <v>8100</v>
       </c>
       <c r="Q4" t="n">
-        <v>18230</v>
+        <v>592</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>블룸에너지 언급하며 매출 성장성 기대. 개인 투자자 매수세.</t>
+          <t>미국 광통신 섹터 급등에 따른 기대감. 글로벌 회사 공급 및 긍정적 재료 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수소에너지', '매출', '개인']</t>
+          <t>['광통신', '급등', '글로벌공급']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>15120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+3.69%</t>
+          <t>+10.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="F5" t="n">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>1104</v>
+        <v>556</v>
       </c>
       <c r="H5" t="n">
-        <v>23.61</v>
+        <v>1.55</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>89500</v>
+        <v>13700</v>
       </c>
       <c r="K5" t="n">
-        <v>92000</v>
+        <v>14260</v>
       </c>
       <c r="L5" t="n">
-        <v>94300</v>
+        <v>15860</v>
       </c>
       <c r="M5" t="n">
-        <v>91300</v>
+        <v>14210</v>
       </c>
       <c r="N5" t="n">
-        <v>23.63</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>71408600250</v>
+        <v>238411826045</v>
       </c>
       <c r="P5" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>57000</v>
+        <v>1252</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
+          <t>단기 박스권 돌파 및 우상향 추세 기대. 광통신 관련 미장 흐름 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가']</t>
+          <t>['광통신', '우상향', '박스권돌파']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35050</v>
+        <v>93700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="G6" t="n">
-        <v>116</v>
+        <v>1211</v>
       </c>
       <c r="H6" t="n">
-        <v>52.79</v>
+        <v>23.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>34100</v>
+        <v>89500</v>
       </c>
       <c r="K6" t="n">
-        <v>34450</v>
+        <v>92000</v>
       </c>
       <c r="L6" t="n">
-        <v>35325</v>
+        <v>94400</v>
       </c>
       <c r="M6" t="n">
-        <v>34050</v>
+        <v>91300</v>
       </c>
       <c r="N6" t="n">
-        <v>21.01</v>
+        <v>23.63</v>
       </c>
       <c r="O6" t="n">
-        <v>16510441075</v>
+        <v>127622223050</v>
       </c>
       <c r="P6" t="n">
-        <v>69500</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>30400</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 25조 선납매 언급. 유가 상승에 따른 기대감.</t>
+          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '선납매', '유가']</t>
+          <t>['원전', 'SMR', '주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20450</v>
+        <v>20700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+2.40%</t>
+          <t>+3.66%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.38</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="H7" t="n">
         <v>10.85</v>
@@ -1061,7 +1061,7 @@
         <v>20250</v>
       </c>
       <c r="L7" t="n">
-        <v>21200</v>
+        <v>21300</v>
       </c>
       <c r="M7" t="n">
         <v>20050</v>
@@ -1070,7 +1070,7 @@
         <v>10.47</v>
       </c>
       <c r="O7" t="n">
-        <v>59774083500</v>
+        <v>106119797075</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 대형 원전 건설 참여 가능성 언급. 역대 거래량으로 장기 매물 흡수.</t>
+          <t>미국 원전 참여 기대감 속 거래량 증가. 이란 관련 이슈와 유가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '거래량', '건설']</t>
+          <t>['원전', '거래량', '이란']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12070</v>
+        <v>30700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+3.19%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.16</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="G8" t="n">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11990</v>
+        <v>29750</v>
       </c>
       <c r="K8" t="n">
-        <v>12440</v>
+        <v>31600</v>
       </c>
       <c r="L8" t="n">
-        <v>12800</v>
+        <v>34200</v>
       </c>
       <c r="M8" t="n">
-        <v>12000</v>
+        <v>30500</v>
       </c>
       <c r="N8" t="n">
-        <v>2.16</v>
+        <v>0.23</v>
       </c>
       <c r="O8" t="n">
-        <v>16520125245</v>
+        <v>155325823100</v>
       </c>
       <c r="P8" t="n">
-        <v>36200</v>
+        <v>39350</v>
       </c>
       <c r="Q8" t="n">
-        <v>8920</v>
+        <v>8200</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 리스크 언급. 주가 상승 기대.</t>
+          <t>상장 폐지 관련 우려와 함께 상승 기대감 혼재. 기술적 분석 및 거래 대금 중요성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유가', '전쟁', '지정학']</t>
+          <t>['상장폐지', '기술적분석', '거래대금']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,97 +1200,373 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>269500</v>
+        <v>12330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>-2.16</v>
       </c>
       <c r="E9" t="n">
-        <v>691</v>
+        <v>96</v>
       </c>
       <c r="F9" t="n">
-        <v>392</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>2732</v>
+        <v>205</v>
       </c>
       <c r="H9" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>269500</v>
+        <v>11990</v>
       </c>
       <c r="K9" t="n">
-        <v>269500</v>
+        <v>12440</v>
       </c>
       <c r="L9" t="n">
-        <v>270500</v>
+        <v>12800</v>
       </c>
       <c r="M9" t="n">
-        <v>268500</v>
+        <v>11920</v>
       </c>
       <c r="N9" t="n">
-        <v>46.79</v>
+        <v>2.16</v>
       </c>
       <c r="O9" t="n">
-        <v>429755191250</v>
+        <v>23752552365</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>36200</v>
       </c>
       <c r="Q9" t="n">
-        <v>70000</v>
+        <v>8920</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 반도체주 상승 소식에 삼성전자 10% 상승 기대감 표출. 구체적인 근거 제시 부족.</t>
+          <t>국제 유가 급등 및 지정학적 리스크 부각으로 인한 주가 상승 기대감. 이란 관련 뉴스 다수.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['국제유가', '전쟁', '이란']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>34850</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+2.20%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>0.1</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>['반도체', 'AI', '주가']</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
+      <c r="E10" t="n">
+        <v>52</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
+        <v>144</v>
+      </c>
+      <c r="H10" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>34100</v>
+      </c>
+      <c r="K10" t="n">
+        <v>34450</v>
+      </c>
+      <c r="L10" t="n">
+        <v>35325</v>
+      </c>
+      <c r="M10" t="n">
+        <v>34050</v>
+      </c>
+      <c r="N10" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="O10" t="n">
+        <v>28771066725</v>
+      </c>
+      <c r="P10" t="n">
+        <v>69500</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>30400</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-46000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>유가 상승 및 미국 원전 협력 기대감 속에서 발전 5사 통합 긍정적 전망. 공매도 세력에 대한 경계감.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['원전', '발전', '유가']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8960</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>192</v>
+      </c>
+      <c r="H11" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8940</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8990</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8710</v>
+      </c>
+      <c r="N11" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7224664160</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17950</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8120</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-245000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>중국산 제품 경쟁 심화 및 유증 가능성 언급. 주가 관리 능력에 대한 부정적 의견.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['중국산', '유증', '주가관리']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>269750</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>794</v>
+      </c>
+      <c r="F12" t="n">
+        <v>444</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2922</v>
+      </c>
+      <c r="H12" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>269500</v>
+      </c>
+      <c r="K12" t="n">
+        <v>269500</v>
+      </c>
+      <c r="L12" t="n">
+        <v>272000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>268500</v>
+      </c>
+      <c r="N12" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="O12" t="n">
+        <v>748886359250</v>
+      </c>
+      <c r="P12" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>70000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-689000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>AI 및 반도체 산업 관련 뉴스 언급. 30만 전자 및 국내 정치 관련 논의.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['반도체', 'AI', '30만전자']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>102</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>005930</t>
         </is>

--- a/data/trending_integrated_20260909_09.xlsx
+++ b/data/trending_integrated_20260909_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13300</v>
+        <v>6570</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+12.62%</t>
+          <t>+29.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>382</v>
+        <v>147</v>
       </c>
       <c r="H2" t="n">
-        <v>5.64</v>
+        <v>2.46</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11810</v>
+        <v>5060</v>
       </c>
       <c r="K2" t="n">
-        <v>12050</v>
+        <v>5190</v>
       </c>
       <c r="L2" t="n">
-        <v>13990</v>
+        <v>6570</v>
       </c>
       <c r="M2" t="n">
-        <v>11950</v>
+        <v>5110</v>
       </c>
       <c r="N2" t="n">
-        <v>5.42</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>119536095005</v>
+        <v>32756958435</v>
       </c>
       <c r="P2" t="n">
-        <v>30200</v>
+        <v>16200</v>
       </c>
       <c r="Q2" t="n">
-        <v>3540</v>
+        <v>1206</v>
       </c>
       <c r="R2" t="n">
-        <v>731000</v>
+        <v>144000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>원전 및 로봇 섹터 주도주 전망. 미국 원전 관련 뉴스 및 소형원자로 배치 언급.</t>
+          <t>신규 상장 후 주가 상승 기대감 높음. 매집 및 대장주 역할 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '소형원자로']</t>
+          <t>['신규상장', '매집', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55200</v>
+        <v>57300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+12.08%</t>
+          <t>+16.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="H3" t="n">
         <v>14.96</v>
@@ -693,7 +693,7 @@
         <v>53500</v>
       </c>
       <c r="L3" t="n">
-        <v>55900</v>
+        <v>57600</v>
       </c>
       <c r="M3" t="n">
         <v>51600</v>
@@ -702,7 +702,7 @@
         <v>14.93</v>
       </c>
       <c r="O3" t="n">
-        <v>47421466300</v>
+        <v>63886117400</v>
       </c>
       <c r="P3" t="n">
         <v>108900</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인 매도세 속 목표가 상향 및 성장성 기대. 수소 에너지 관련 언급.</t>
+          <t>외인 매도세 속 연기금 매수 기대. 블룸에너지, 범한퓨얼셀 등 경쟁사 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['수소에너지', '목표가', '성장성']</t>
+          <t>['청정에너지', '연기금', '블룸에너지']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4025</v>
+        <v>13300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.58%</t>
+          <t>+12.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.74</v>
+        <v>0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>228</v>
+        <v>432</v>
       </c>
       <c r="H4" t="n">
-        <v>3.19</v>
+        <v>5.64</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3640</v>
+        <v>11810</v>
       </c>
       <c r="K4" t="n">
-        <v>3750</v>
+        <v>12050</v>
       </c>
       <c r="L4" t="n">
-        <v>4460</v>
+        <v>13990</v>
       </c>
       <c r="M4" t="n">
-        <v>3680</v>
+        <v>11950</v>
       </c>
       <c r="N4" t="n">
-        <v>0.45</v>
+        <v>5.42</v>
       </c>
       <c r="O4" t="n">
-        <v>181903605956</v>
+        <v>134782365715</v>
       </c>
       <c r="P4" t="n">
-        <v>8100</v>
+        <v>30200</v>
       </c>
       <c r="Q4" t="n">
-        <v>592</v>
+        <v>3540</v>
       </c>
       <c r="R4" t="n">
-        <v>282000</v>
+        <v>731000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 급등에 따른 기대감. 글로벌 회사 공급 및 긍정적 재료 언급.</t>
+          <t>원전 로봇 하반기 주도주 전망. 미국 원전 관련 호재 및 외국 자본 유입 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '급등', '글로벌공급']</t>
+          <t>['원전', '로봇', '외국자본']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15120</v>
+        <v>15190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.36%</t>
+          <t>+10.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="H5" t="n">
         <v>1.55</v>
@@ -886,7 +886,7 @@
         <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>238411826045</v>
+        <v>261727855620</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 우상향 추세 기대. 광통신 관련 미장 흐름 언급.</t>
+          <t>미국 광통신 관련주 급등에 따른 기대감. 외국인 대량 순매수 및 거래대금 증가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '우상향', '박스권돌파']</t>
+          <t>['광통신', '외국인', '거래대금']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93700</v>
+        <v>4025</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+4.69%</t>
+          <t>+10.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>2.74</v>
       </c>
       <c r="E6" t="n">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>1211</v>
+        <v>222</v>
       </c>
       <c r="H6" t="n">
-        <v>23.61</v>
+        <v>3.19</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>89500</v>
+        <v>3640</v>
       </c>
       <c r="K6" t="n">
-        <v>92000</v>
+        <v>3750</v>
       </c>
       <c r="L6" t="n">
-        <v>94400</v>
+        <v>4460</v>
       </c>
       <c r="M6" t="n">
-        <v>91300</v>
+        <v>3680</v>
       </c>
       <c r="N6" t="n">
-        <v>23.63</v>
+        <v>0.45</v>
       </c>
       <c r="O6" t="n">
-        <v>127622223050</v>
+        <v>197111758802</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>36000</v>
+        <v>282000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
+          <t>미국 광통신 개폭등 및 글로벌 회사 대량 공급 뉴스. 투자경고 종목 지정 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가']</t>
+          <t>['광통신', '재료', '투자경고']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20700</v>
+        <v>8280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+7.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.38</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="H7" t="n">
-        <v>10.85</v>
+        <v>1.81</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19970</v>
+        <v>7680</v>
       </c>
       <c r="K7" t="n">
-        <v>20250</v>
+        <v>7780</v>
       </c>
       <c r="L7" t="n">
-        <v>21300</v>
+        <v>9000</v>
       </c>
       <c r="M7" t="n">
-        <v>20050</v>
+        <v>7750</v>
       </c>
       <c r="N7" t="n">
-        <v>10.47</v>
+        <v>0.41</v>
       </c>
       <c r="O7" t="n">
-        <v>106119797075</v>
+        <v>59420667735</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>10300</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>952</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 원전 참여 기대감 속 거래량 증가. 이란 관련 이슈와 유가 상승 가능성 언급.</t>
+          <t>시멘트 기초 작업 시작 및 추석까지 실적 기대감. 외인 대량 매수 및 5% 이상 상승.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '거래량', '이란']</t>
+          <t>['시멘트', '실적', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30700</v>
+        <v>31350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>+5.38%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="F8" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G8" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="H8" t="n">
         <v>0.31</v>
@@ -1162,7 +1162,7 @@
         <v>0.23</v>
       </c>
       <c r="O8" t="n">
-        <v>155325823100</v>
+        <v>172625449525</v>
       </c>
       <c r="P8" t="n">
         <v>39350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장 폐지 관련 우려와 함께 상승 기대감 혼재. 기술적 분석 및 거래 대금 중요성 언급.</t>
+          <t>상장 폐지 가능성 언급 속 기술적 반등 기대감 공존. 시외 거래 및 기준봉 존재 근거 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상장폐지', '기술적분석', '거래대금']</t>
+          <t>['기준봉', '시외거래', '기술적반등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12330</v>
+        <v>93100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+4.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>1230</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11990</v>
+        <v>89500</v>
       </c>
       <c r="K9" t="n">
-        <v>12440</v>
+        <v>92000</v>
       </c>
       <c r="L9" t="n">
-        <v>12800</v>
+        <v>94400</v>
       </c>
       <c r="M9" t="n">
-        <v>11920</v>
+        <v>91300</v>
       </c>
       <c r="N9" t="n">
-        <v>2.16</v>
+        <v>23.63</v>
       </c>
       <c r="O9" t="n">
-        <v>23752552365</v>
+        <v>144442199350</v>
       </c>
       <c r="P9" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>34000</v>
+        <v>36000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 리스크 부각으로 인한 주가 상승 기대감. 이란 관련 뉴스 다수.</t>
+          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁', '이란']</t>
+          <t>['원전', 'SMR', '주가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34850</v>
+        <v>20650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.20%</t>
+          <t>+3.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>144</v>
+        <v>327</v>
       </c>
       <c r="H10" t="n">
-        <v>52.75</v>
+        <v>10.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>34100</v>
+        <v>19970</v>
       </c>
       <c r="K10" t="n">
-        <v>34450</v>
+        <v>20250</v>
       </c>
       <c r="L10" t="n">
-        <v>35325</v>
+        <v>21300</v>
       </c>
       <c r="M10" t="n">
-        <v>34050</v>
+        <v>20050</v>
       </c>
       <c r="N10" t="n">
-        <v>21.01</v>
+        <v>10.47</v>
       </c>
       <c r="O10" t="n">
-        <v>28771066725</v>
+        <v>114561315700</v>
       </c>
       <c r="P10" t="n">
-        <v>69500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>30400</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-46000</v>
+        <v>-693000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유가 상승 및 미국 원전 협력 기대감 속에서 발전 5사 통합 긍정적 전망. 공매도 세력에 대한 경계감.</t>
+          <t>미국 원전 참여 기대감 속 거래량 증가. 이란 관련 불확실성과 개미 털기 경고.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '발전', '유가']</t>
+          <t>['원전', '거래량', '매물']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8960</v>
+        <v>34750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.36</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="H11" t="n">
-        <v>27.69</v>
+        <v>52.74</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8940</v>
+        <v>34100</v>
       </c>
       <c r="K11" t="n">
-        <v>8940</v>
+        <v>34450</v>
       </c>
       <c r="L11" t="n">
-        <v>8990</v>
+        <v>35325</v>
       </c>
       <c r="M11" t="n">
-        <v>8710</v>
+        <v>34050</v>
       </c>
       <c r="N11" t="n">
-        <v>28.05</v>
+        <v>21.01</v>
       </c>
       <c r="O11" t="n">
-        <v>7224664160</v>
+        <v>33555199850</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>69500</v>
       </c>
       <c r="Q11" t="n">
-        <v>8120</v>
+        <v>30400</v>
       </c>
       <c r="R11" t="n">
-        <v>-245000</v>
+        <v>-46000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>중국산 제품 경쟁 심화 및 유증 가능성 언급. 주가 관리 능력에 대한 부정적 의견.</t>
+          <t>미국 원전 협력 기대감 및 발전 5사 통합 긍정적. Smp 급락 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['중국산', '유증', '주가관리']</t>
+          <t>['원전', 'SMP', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>269750</v>
+        <v>12210</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>-2.16</v>
       </c>
       <c r="E12" t="n">
-        <v>794</v>
+        <v>101</v>
       </c>
       <c r="F12" t="n">
-        <v>444</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>2922</v>
+        <v>216</v>
       </c>
       <c r="H12" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>269500</v>
+        <v>11990</v>
       </c>
       <c r="K12" t="n">
-        <v>269500</v>
+        <v>12440</v>
       </c>
       <c r="L12" t="n">
-        <v>272000</v>
+        <v>12800</v>
       </c>
       <c r="M12" t="n">
-        <v>268500</v>
+        <v>11920</v>
       </c>
       <c r="N12" t="n">
-        <v>46.79</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
-        <v>748886359250</v>
+        <v>25833368905</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>70000</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>-689000</v>
+        <v>34000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 및 반도체 산업 관련 뉴스 언급. 30만 전자 및 국내 정치 관련 논의.</t>
+          <t>국제 유가 급등 및 지정학적 리스크 부각으로 인한 주가 상승 기대감. 이란 관련 뉴스 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,18 +1555,294 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '30만전자']</t>
+          <t>['국제유가', '전쟁', '이란']</t>
         </is>
       </c>
       <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1824500</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>+1.76%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E13" t="n">
+        <v>796</v>
+      </c>
+      <c r="F13" t="n">
+        <v>424</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2734</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1793000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1795000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1795000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1321786716500</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>277000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-27000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>JP모건의 심각한 저평가 분석 제시. 미국 증시 및 ADR 급등에 따른 200 돌파 기대감.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['반도체', '저평가', 'ADR']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8980</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>+0.45%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E14" t="n">
+        <v>49</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>207</v>
+      </c>
+      <c r="H14" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8940</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8710</v>
+      </c>
+      <c r="N14" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8221830470</v>
+      </c>
+      <c r="P14" t="n">
+        <v>17950</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8120</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-245000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>본격적인 성장 국면 진입 기대에도 불구하고 중국산 영향 및 3분기 실적 악화 우려. 주가 관리 무능력 비판.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['디스플레이', '실적', '환율']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>270000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>793</v>
+      </c>
+      <c r="F15" t="n">
+        <v>440</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2616</v>
+      </c>
+      <c r="H15" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>269500</v>
+      </c>
+      <c r="K15" t="n">
+        <v>269500</v>
+      </c>
+      <c r="L15" t="n">
+        <v>272000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>268500</v>
+      </c>
+      <c r="N15" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="O15" t="n">
+        <v>875386477750</v>
+      </c>
+      <c r="P15" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>70000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-689000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>미국 반도체(인텔) 폭등에 따른 기대감. 개인의 저가 매수 유입.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['반도체', 'AI', '인텔']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>102</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>005930</t>
         </is>

--- a/data/trending_integrated_20260909_09.xlsx
+++ b/data/trending_integrated_20260909_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="H2" t="n">
         <v>2.46</v>
@@ -610,7 +610,7 @@
         <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>32756958435</v>
+        <v>33282223365</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -619,14 +619,14 @@
         <v>1206</v>
       </c>
       <c r="R2" t="n">
-        <v>144000</v>
+        <v>84000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장 후 주가 상승 기대감 높음. 매집 및 대장주 역할 가능성 언급.</t>
+          <t>주주들의 기다림 끝에 상승세 예상, 단기 고점 및 상장 기대감 존재. 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장', '매집', '대장주']</t>
+          <t>['상장', '단기 고점', '매집']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57300</v>
+        <v>57500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+16.35%</t>
+          <t>+16.75%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H3" t="n">
         <v>14.96</v>
@@ -693,7 +693,7 @@
         <v>53500</v>
       </c>
       <c r="L3" t="n">
-        <v>57600</v>
+        <v>58200</v>
       </c>
       <c r="M3" t="n">
         <v>51600</v>
@@ -702,7 +702,7 @@
         <v>14.93</v>
       </c>
       <c r="O3" t="n">
-        <v>63886117400</v>
+        <v>79329483800</v>
       </c>
       <c r="P3" t="n">
         <v>108900</v>
@@ -711,14 +711,14 @@
         <v>18230</v>
       </c>
       <c r="R3" t="n">
-        <v>-198000</v>
+        <v>-232000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인 매도세 속 연기금 매수 기대. 블룸에너지, 범한퓨얼셀 등 경쟁사 부각.</t>
+          <t>두산퓨얼셀의 성장성 및 목표가 상향 기대감. 블룸에너지, 범한퓨얼셀 언급 및 연기금/기관 매수 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['청정에너지', '연기금', '블룸에너지']</t>
+          <t>['두산퓨얼셀', '청정에너지', '블룸에너지']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13300</v>
+        <v>13700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+12.62%</t>
+          <t>+16.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="H4" t="n">
         <v>5.64</v>
@@ -794,7 +794,7 @@
         <v>5.42</v>
       </c>
       <c r="O4" t="n">
-        <v>134782365715</v>
+        <v>154908415725</v>
       </c>
       <c r="P4" t="n">
         <v>30200</v>
@@ -803,23 +803,23 @@
         <v>3540</v>
       </c>
       <c r="R4" t="n">
-        <v>731000</v>
+        <v>553000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>원전 로봇 하반기 주도주 전망. 미국 원전 관련 호재 및 외국 자본 유입 기대.</t>
+          <t>우리기술의 원전 관련주 대장주 부상 및 급등 전망. 사우디, 미국 원전 관련 뉴스 및 정부 정책 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '외국자본']</t>
+          <t>['우리기술', '원전', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15190</v>
+        <v>14920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.88%</t>
+          <t>+8.91%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>570</v>
+        <v>611</v>
       </c>
       <c r="H5" t="n">
         <v>1.55</v>
@@ -886,7 +886,7 @@
         <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>261727855620</v>
+        <v>275492112085</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -895,23 +895,23 @@
         <v>1252</v>
       </c>
       <c r="R5" t="n">
-        <v>500000</v>
+        <v>559000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등에 따른 기대감. 외국인 대량 순매수 및 거래대금 증가.</t>
+          <t>대한광통신의 단기 박스권 돌파 및 우상향 추세 전망. 거래대금 상위, 외국인 순매수, 공매도 감소 등 긍정적 지표 포함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '외국인', '거래대금']</t>
+          <t>['대한광통신', '광통신', '우상향']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4025</v>
+        <v>3890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.58%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2.74</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="H6" t="n">
         <v>3.19</v>
@@ -978,7 +978,7 @@
         <v>0.45</v>
       </c>
       <c r="O6" t="n">
-        <v>197111758802</v>
+        <v>210247609163</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -987,23 +987,23 @@
         <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>282000</v>
+        <v>-15000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신 개폭등 및 글로벌 회사 대량 공급 뉴스. 투자경고 종목 지정 우려.</t>
+          <t>미국 광통신주 급등에 따른 빛과전자 상한가 기대감. 글로벌 회사 대량 공급 뉴스 및 골드만삭스 자료 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '재료', '투자경고']</t>
+          <t>['빛과전자', '광통신', '글로벌']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8280</v>
+        <v>8170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.81%</t>
+          <t>+6.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.4</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="H7" t="n">
         <v>1.81</v>
@@ -1070,7 +1070,7 @@
         <v>0.41</v>
       </c>
       <c r="O7" t="n">
-        <v>59420667735</v>
+        <v>64469157170</v>
       </c>
       <c r="P7" t="n">
         <v>10300</v>
@@ -1079,23 +1079,23 @@
         <v>952</v>
       </c>
       <c r="R7" t="n">
-        <v>105000</v>
+        <v>-73000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>시멘트 기초 작업 시작 및 추석까지 실적 기대감. 외인 대량 매수 및 5% 이상 상승.</t>
+          <t>서산의 시멘트 업종 및 건설 관련 기대감. 대장주로서의 움직임 및 외인 대량 매수 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['시멘트', '실적', '외인']</t>
+          <t>['서산', '시멘트', '건설']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31350</v>
+        <v>2040</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.38%</t>
+          <t>+6.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29750</v>
+        <v>1922</v>
       </c>
       <c r="K8" t="n">
-        <v>31600</v>
+        <v>1920</v>
       </c>
       <c r="L8" t="n">
-        <v>34200</v>
+        <v>2090</v>
       </c>
       <c r="M8" t="n">
-        <v>30500</v>
+        <v>1862</v>
       </c>
       <c r="N8" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="O8" t="n">
-        <v>172625449525</v>
+        <v>3692179070</v>
       </c>
       <c r="P8" t="n">
-        <v>39350</v>
+        <v>2930</v>
       </c>
       <c r="Q8" t="n">
-        <v>8200</v>
+        <v>910</v>
       </c>
       <c r="R8" t="n">
-        <v>1000</v>
+        <v>29000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장 폐지 가능성 언급 속 기술적 반등 기대감 공존. 시외 거래 및 기준봉 존재 근거 언급.</t>
+          <t>대주주 매도 공시 핑계 하락 후, 광주 개발 및 나대지 가치 상승 등 대규모 재료 공시 기대. 2차 파동 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기준봉', '시외거래', '기술적반등']</t>
+          <t>['대주주 매도', '재료 공시', '나대지 가치']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93100</v>
+        <v>31000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.02%</t>
+          <t>+4.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>234</v>
       </c>
       <c r="F9" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="G9" t="n">
-        <v>1230</v>
+        <v>296</v>
       </c>
       <c r="H9" t="n">
-        <v>23.61</v>
+        <v>0.31</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>89500</v>
+        <v>29750</v>
       </c>
       <c r="K9" t="n">
-        <v>92000</v>
+        <v>31600</v>
       </c>
       <c r="L9" t="n">
-        <v>94400</v>
+        <v>34200</v>
       </c>
       <c r="M9" t="n">
-        <v>91300</v>
+        <v>30500</v>
       </c>
       <c r="N9" t="n">
-        <v>23.63</v>
+        <v>0.23</v>
       </c>
       <c r="O9" t="n">
-        <v>144442199350</v>
+        <v>179095113300</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>39350</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>8200</v>
       </c>
       <c r="R9" t="n">
-        <v>36000</v>
+        <v>3000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
+          <t>상장 폐지 우려와 함께 시외 상승 및 기술적 반등 기대감이 혼재하나, 하락 시작 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가']</t>
+          <t>['상폐', '기준봉', '기술적 반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20650</v>
+        <v>92700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.41%</t>
+          <t>+3.58%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.38</v>
+        <v>-0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="G10" t="n">
-        <v>327</v>
+        <v>1291</v>
       </c>
       <c r="H10" t="n">
-        <v>10.85</v>
+        <v>23.61</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19970</v>
+        <v>89500</v>
       </c>
       <c r="K10" t="n">
-        <v>20250</v>
+        <v>92000</v>
       </c>
       <c r="L10" t="n">
-        <v>21300</v>
+        <v>94400</v>
       </c>
       <c r="M10" t="n">
-        <v>20050</v>
+        <v>91300</v>
       </c>
       <c r="N10" t="n">
-        <v>10.47</v>
+        <v>23.63</v>
       </c>
       <c r="O10" t="n">
-        <v>114561315700</v>
+        <v>154874798300</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-693000</v>
+        <v>113000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 원전 참여 기대감 속 거래량 증가. 이란 관련 불확실성과 개미 털기 경고.</t>
+          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '거래량', '매물']</t>
+          <t>['원전', 'SMR', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34750</v>
+        <v>1846000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+2.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>794</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>430</v>
       </c>
       <c r="G11" t="n">
-        <v>158</v>
+        <v>2496</v>
       </c>
       <c r="H11" t="n">
-        <v>52.74</v>
+        <v>50.66</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34100</v>
+        <v>1793000</v>
       </c>
       <c r="K11" t="n">
-        <v>34450</v>
+        <v>1795000</v>
       </c>
       <c r="L11" t="n">
-        <v>35325</v>
+        <v>1849000</v>
       </c>
       <c r="M11" t="n">
-        <v>34050</v>
+        <v>1795000</v>
       </c>
       <c r="N11" t="n">
-        <v>21.01</v>
+        <v>50.63</v>
       </c>
       <c r="O11" t="n">
-        <v>33555199850</v>
+        <v>1575741199000</v>
       </c>
       <c r="P11" t="n">
-        <v>69500</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>30400</v>
+        <v>277000</v>
       </c>
       <c r="R11" t="n">
-        <v>-46000</v>
+        <v>3000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 원전 협력 기대감 및 발전 5사 통합 긍정적. Smp 급락 및 공매도 우려.</t>
+          <t>SK하이닉스의 200돌파 기대감 및 미국채 금리 하락 영향. 반도체 업종 내에서 삼성전자 대비 우위 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', 'SMP', '공매도']</t>
+          <t>['SK하이닉스', '반도체', '미국채']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12210</v>
+        <v>20500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2.16</v>
+        <v>0.38</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>216</v>
+        <v>368</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11990</v>
+        <v>19970</v>
       </c>
       <c r="K12" t="n">
-        <v>12440</v>
+        <v>20250</v>
       </c>
       <c r="L12" t="n">
-        <v>12800</v>
+        <v>21300</v>
       </c>
       <c r="M12" t="n">
-        <v>11920</v>
+        <v>20050</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>10.47</v>
       </c>
       <c r="O12" t="n">
-        <v>25833368905</v>
+        <v>119696056550</v>
       </c>
       <c r="P12" t="n">
-        <v>36200</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>8920</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>34000</v>
+        <v>-974000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 리스크 부각으로 인한 주가 상승 기대감. 이란 관련 뉴스 다수.</t>
+          <t>미국 원전 관련주 상승에 따른 기대감 및 대우건설 언급. 이란 항복, 유가 상승 등의 외부 요인도 거론됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁', '이란']</t>
+          <t>['원전', '대우건설', '미국']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1824500</v>
+        <v>34600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>796</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>2734</v>
+        <v>165</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>52.73</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>34100</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>34450</v>
       </c>
       <c r="L13" t="n">
-        <v>1840000</v>
+        <v>35325</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>34050</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>21.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1321786716500</v>
+        <v>36722512425</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>69500</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>30400</v>
       </c>
       <c r="R13" t="n">
-        <v>-27000</v>
+        <v>7000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>JP모건의 심각한 저평가 분석 제시. 미국 증시 및 ADR 급등에 따른 200 돌파 기대감.</t>
+          <t>한국전력의 주가 상승 기대감 및 미국 원전 협력 가능성 언급. 발전 5사 통합 및 선납매 관련 내용도 포함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '저평가', 'ADR']</t>
+          <t>['한국전력', '원전', 'Smp']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8980</v>
+        <v>12100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.36</v>
+        <v>-2.16</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="H14" t="n">
-        <v>27.69</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8940</v>
+        <v>11990</v>
       </c>
       <c r="K14" t="n">
-        <v>8940</v>
+        <v>12440</v>
       </c>
       <c r="L14" t="n">
-        <v>9000</v>
+        <v>12800</v>
       </c>
       <c r="M14" t="n">
-        <v>8710</v>
+        <v>11920</v>
       </c>
       <c r="N14" t="n">
-        <v>28.05</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
-        <v>8221830470</v>
+        <v>26987687415</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R14" t="n">
-        <v>-245000</v>
+        <v>37000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>본격적인 성장 국면 진입 기대에도 불구하고 중국산 영향 및 3분기 실적 악화 우려. 주가 관리 무능력 비판.</t>
+          <t>국제 유가 급등에 따른 기대감 고조, 100달러 돌파 및 지정학적 리스크 언급. 외인 매도세 주의.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['디스플레이', '실적', '환율']</t>
+          <t>['국제 유가', '지정학적 리스크', '외인 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>270000</v>
+        <v>271500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="F15" t="n">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="G15" t="n">
-        <v>2616</v>
+        <v>2552</v>
       </c>
       <c r="H15" t="n">
         <v>46.85</v>
@@ -1806,7 +1806,7 @@
         <v>46.79</v>
       </c>
       <c r="O15" t="n">
-        <v>875386477750</v>
+        <v>980221751000</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,10 +1815,10 @@
         <v>70000</v>
       </c>
       <c r="R15" t="n">
-        <v>-689000</v>
+        <v>-467000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1845,6 +1845,190 @@
       <c r="Z15" t="inlineStr">
         <is>
           <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>8980</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>+0.45%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="n">
+        <v>34</v>
+      </c>
+      <c r="G16" t="n">
+        <v>255</v>
+      </c>
+      <c r="H16" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8940</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9030</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8710</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9027832295</v>
+      </c>
+      <c r="P16" t="n">
+        <v>17950</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8120</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-209000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>LG디스플레이의 성장성 및 목표가 하향에 대한 부정적 전망. 중국산 경쟁 심화 및 외인 매도 관련 내용 포함.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['LG디스플레이', '중국산', '매각']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10470</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E17" t="n">
+        <v>42</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>112</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>10440</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10180</v>
+      </c>
+      <c r="L17" t="n">
+        <v>11340</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10100</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O17" t="n">
+        <v>101996324330</v>
+      </c>
+      <c r="P17" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R17" t="n">
+        <v>34000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>미국 바이오 종목 상승에 대한 기대감 속 현대약품 언급. 다만, 미증시 제약바이오 폭락 및 종목 내 감정적 표현이 다수.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['미프진', '제약바이오', '신고가']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>004310</t>
         </is>
       </c>
     </row>
